--- a/files/SALIK_Valuation_Model_11072026_public.xlsx
+++ b/files/SALIK_Valuation_Model_11072026_public.xlsx
@@ -872,7 +872,7 @@
     <row r="45">
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Step 0 (5-yr walk-forward, h=60, carry-anchored benchmark): 11 non-overlapping windows,</t>
+          <t>the calibration back-test (5-yr walk-forward, h=60, carry-anchored benchmark): 11 non-overlapping windows,</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   EBITDA margin</t>
+          <t xml:space="preserve">  EBITDA margin</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -1324,7 +1324,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   net margin</t>
+          <t xml:space="preserve">  net margin</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -1498,7 +1498,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Total assets  [SOURCED]</t>
+          <t>Total assets [SOURCED]</t>
         </is>
       </c>
       <c r="B4" s="28" t="n">
@@ -1511,7 +1511,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   of which: concession intangible, gross</t>
+          <t xml:space="preserve">  of which: concession intangible, gross</t>
         </is>
       </c>
       <c r="B5" s="28" t="n">
@@ -1527,7 +1527,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   less accumulated amortisation (derived)</t>
+          <t xml:space="preserve">  less accumulated amortisation (derived)</t>
         </is>
       </c>
       <c r="B6" s="28" t="n">
@@ -1543,7 +1543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   concession intangible, net (derived)</t>
+          <t xml:space="preserve">  concession intangible, net (derived)</t>
         </is>
       </c>
       <c r="B7" s="28" t="n">
@@ -1559,7 +1559,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Net debt  [SOURCED]</t>
+          <t>Net debt [SOURCED]</t>
         </is>
       </c>
       <c r="B8" s="28" t="n">
@@ -1575,7 +1575,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Net working capital  [SOURCED]</t>
+          <t>Net working capital [SOURCED]</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
@@ -1591,7 +1591,7 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Net debt / EBITDA (T12M)  [SOURCED]</t>
+          <t>Net debt / EBITDA (T12M) [SOURCED]</t>
         </is>
       </c>
       <c r="B10" s="49" t="n">
@@ -1674,7 +1674,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>depends on a derived line. Logged to the Fundamental Driver Ledger.</t>
+          <t>depends on a derived line. Logged to the our forecast-assumptions log.</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>FREE CASH FLOW  [FY24 &amp; Q1-26 SOURCED]</t>
+          <t>FREE CASH FLOW [FY24 &amp; Q1-26 SOURCED]</t>
         </is>
       </c>
       <c r="B8" s="28" t="n">
@@ -2324,7 +2324,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ENGINE CONFIG (engine/market_profiles.py is the single source of truth)</t>
+          <t>ENGINE CONFIG (our calibration engine is the single source of truth)</t>
         </is>
       </c>
       <c r="B3" s="6" t="n"/>
@@ -2361,7 +2361,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cone calibration width_cal (fitted)</t>
+          <t>Cone-width calibration (fitted)</t>
         </is>
       </c>
       <c r="B6" s="37" t="n">
@@ -2433,7 +2433,7 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>nu is WEAKLY IDENTIFIED. Never quote it as precise: the (nu, width_cal) PAIR is what is</t>
+          <t>nu is WEAKLY IDENTIFIED. Never quote it as precise: the (nu, the cone-width calibration) PAIR is what is</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>STEP-0 CALIBRATION (the pass-gate; full numbers publish to the Ledger, not to the study)</t>
+          <t>CALIBRATION BACK-TEST (the pass/fail check; full numbers publish to the public Ledger, not to the study)</t>
         </is>
       </c>
       <c r="B43" s="6" t="n"/>
@@ -3279,7 +3279,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>WACC x TERMINAL g (beta held at the house 1.00)</t>
+          <t>WACC x TERMINAL g (beta held at our 1.00)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>THE 0.80 BETA FLOOR — a challenged house rule, priced</t>
+          <t>THE 0.80 BETA FLOOR — a challenged standing rule, priced</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -3517,14 +3517,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Standing Research Protocol says the OPPOSITE: attempt the regression; fall back to 1.0 ONLY</t>
+          <t>The our published research standards says the OPPOSITE: attempt the regression; fall back to 1.0 ONLY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>on a usability-gate FAILURE (n&gt;=24, R2&gt;=5%, SE&lt;|b|). Ours passes all three. wacc_builder.py has</t>
+          <t>on a usability-gate FAILURE (n&gt;=24, R2&gt;=5%, SE&lt;|b|). Ours passes all three. our cost-of-capital module has</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PEER SET, AND THE STEP-2A INFORMATION SWEEP REGISTER</t>
+          <t>PEER SET, AND THE RESEARCH REGISTER</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4358,7 +4358,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>STEP-2A INFORMATION SWEEP REGISTER — four rings, run BEFORE any driver was set</t>
+          <t>RESEARCH REGISTER — four rings, run BEFORE any driver was set</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
@@ -4916,7 +4916,7 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>VALIDATED by engine/research_sweep.py: PASS - 4/4 rings, 21 findings, 13 driver-gate rows, 0 errors, 0 warnings.</t>
+          <t>VALIDATED by our research register: PASS - 4/4 rings, 21 findings, 13 driver-gate rows, 0 errors, 0 warnings.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>Step 0 verdict: PARITY (robust, blocks 2/3/4) · 11 windows · cone OVER-covered</t>
+          <t>the calibration back-test verdict: PARITY (robust, blocks 2/3/4) · 11 windows · cone OVER-covered</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
     <row r="19">
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   -&gt; 5.53%; (c) 3M EIBOR 3.76% + 150-175bp IG term margin = 5.26-5.51%.</t>
+          <t xml:space="preserve">  -&gt; 5.53%; (c) 3M EIBOR 3.76% + 150-175bp IG term margin = 5.26-5.51%.</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>FORWARD DRIVERS — the preparer's judgment, logged to the Driver Ledger</t>
+          <t>FORWARD DRIVERS — the preparer's judgment, logged to the our forecast-assumptions log</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
@@ -6615,7 +6615,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>n=19 &lt; the 24-observation usability floor, so the gate FAILED and the house rule forced beta = 1.00.</t>
+          <t>n=19 &lt; the 24-observation usability floor, so the gate FAILED and our standing rule forced beta = 1.00.</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>every constituent through the same Step-0.0 data-quality gate. The regression now PASSES comfortably.</t>
+          <t>every constituent through the same the data-quality check. The regression now PASSES comfortably.</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>Usability gate</t>
+          <t>Usability test</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which Business Bay Crossing</t>
+          <t xml:space="preserve"> of which Business Bay Crossing</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
@@ -7428,7 +7428,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which Al Safa South</t>
+          <t xml:space="preserve"> of which Al Safa South</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -8082,7 +8082,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ONE-OFF SHARE OF THE GROWTH  (new gates + variable pricing)</t>
+          <t>ONE-OFF SHARE OF THE GROWTH (new gates + variable pricing)</t>
         </is>
       </c>
       <c r="C11" s="41">
@@ -9125,7 +9125,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   EBITDA margin</t>
+          <t xml:space="preserve">  EBITDA margin</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
